--- a/tests/realSuite/Piano-Viaggi_Volley-S3_Tn-Nord-e-Sopramonte_4-dic-25_def3_con-VETTORE-e-CELL/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Volley-S3_Tn-Nord-e-Sopramonte_4-dic-25_def3_con-VETTORE-e-CELL/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,42 +436,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IC ALA</t>
+          <t>Centro Sportivo Sopramonte</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ala, Via Betta 9</t>
+          <t>Sopramonte - Via di Mura 11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC ALDENO MATTARELLO</t>
+          <t>Centro Sportivo Tn Nord - Gardolo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mattarello, Via Torre Franca (fermata bus "Al Parco")</t>
+          <t>Gardolo - Via 4 Novembre 23/4</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC ALTA VAL DI SOLE</t>
+          <t>IC ALA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ossana - SSPG - Via San Michele, 11</t>
+          <t>Ala, Via Betta 9</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -481,27 +481,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC ARCO</t>
+          <t>IC ALDENO MATTARELLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arco, park Foro Borio</t>
+          <t>Mattarello, Via Torre Franca (fermata bus "Al Parco")</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC AVIO</t>
+          <t>IC ALTA VAL DI SOLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Avio, Viale A. Degasperi, 69</t>
+          <t>Ossana - SSPG - Via San Michele, 11</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -511,42 +511,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC BASSA ANAUNIA TUENNO</t>
+          <t>IC ARCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tuenno - SSPG – V.le D'Anaunia, Via Maistrelli 11</t>
+          <t>Arco, park Foro Borio</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC BASSA ANAUNIA-TUENNO</t>
+          <t>IC ARCO GARDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tuenno - SSPG – V.le D'Anaunia, Via Maistrelli 11</t>
+          <t>Arco, park Foro Borio</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC BASSA VAL DI SOLE</t>
+          <t>IC AVIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Malé, Nuova stazione FTM</t>
+          <t>Avio, Viale A. Degasperi, 69</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -556,12 +556,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC CHIESE (cadetti)</t>
+          <t>IC BASSA ANAUNIA TUENNO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pieve di Bono, Via Fiera 1 loc. Creto</t>
+          <t>Tuenno - SSPG – V.le D'Anaunia, Via Maistrelli 11</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -571,42 +571,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC CLES</t>
+          <t>IC BASSA ANAUNIA-TUENNO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cles, Piazza Fiera</t>
+          <t>Tuenno - SSPG – V.le D'Anaunia, Via Maistrelli 11</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC FOLGARIA LAVARONE</t>
+          <t>IC BASSA VAL DI SOLE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Folgaria, park Palaghiaccio</t>
+          <t>Malé, Nuova stazione FTM</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC FOLGARIA LAVARONE</t>
+          <t>IC CHIESE (cadetti)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lavarone, Frazione Gionghi, 107/6</t>
+          <t>Pieve di Bono, Via Fiera 1 loc. Creto</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -616,12 +616,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC FONDO REVO'</t>
+          <t>IC CLES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Novella, Fermata Bus VVF, Via Canestrini</t>
+          <t>Cles, Piazza Fiera</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -631,117 +631,117 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC GIUDICARIE ESTERIORI</t>
+          <t>IC FOLGARIA LAVARONE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Comano Terme, Via San Giovanni Bosco 14</t>
+          <t>Folgaria, park Palaghiaccio</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC ISERA ROVERETO</t>
+          <t>IC FOLGARIA LAVARONE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rovereto - Viale della Vittoria, 43</t>
+          <t>Lavarone, Frazione Gionghi, 107/6</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC LAVIS</t>
+          <t>IC FONDO REVO'</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lavis, Via Sette 13/a</t>
+          <t>Novella, Fermata Bus VVF, Via Canestrini</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mezzolombardo, Via degli Alpini 17</t>
+          <t>Comano Terme, Via San Giovanni Bosco 14</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO</t>
+          <t>IC ISERA ROVERETO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Spormaggiore, Via Alt Spaur, 5</t>
+          <t>Rovereto - Viale della Vittoria, 43</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC LAVIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pergine Valsugana, Via Caduti, 39</t>
+          <t>Lavis, Via Sette 13/a</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC PRIMIERO</t>
+          <t>IC MEZZOLOMBARDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USL Tonadico, Via Roma 1 – Primiero SMC</t>
+          <t>Mezzolombardo, Via degli Alpini 17</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC RIVA 1 (cadetti)</t>
+          <t>IC MEZZOLOMBARDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Riva del Garda, piazzale centro Sportivo Malossini, Via delle Ginestre 3</t>
+          <t>Spormaggiore, Via Alt Spaur, 5</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -751,12 +751,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC ROVERETO EST</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rovereto, P.le Orsi – Fermata corriere davanti IPIA Veronesi</t>
+          <t>Pergine Valsugana, Via Caduti, 39</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -766,90 +766,210 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IC ROVERETO SUD</t>
+          <t>IC PRIMIERO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rovereto, Parcheggio Ronchi</t>
+          <t>USL Tonadico, Via Roma 1 – Primiero SMC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC RIVA 1 (cadetti)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Coredo, Piazza della Chiesa</t>
+          <t>Riva del Garda, piazzale centro Sportivo Malossini, Via delle Ginestre 3</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC RIVA 2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Taio, Piazza della Chiesa</t>
+          <t>Riva del Garda, piazzale centro Sportivo Malossini, Via delle Ginestre 3</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC ROVERETO EST</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Roncone, Via Nazionale 20</t>
+          <t>Rovereto, P.le Orsi – Fermata corriere davanti IPIA Veronesi</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC ROVERETO NORD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tione, Via Circonvalazione 44</t>
+          <t>Rovereto, P.le Orsi – Fermata corriere davanti IPIA Veronesi</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>IC ROVERETO SUD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rovereto, Parcheggio Ronchi</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>IC TAIO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Coredo, Piazza della Chiesa</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IC TAIO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Taio, Piazza della Chiesa</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IC TIONE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Roncone, Via Nazionale 20</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>IC TIONE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tione, Via Circonvalazione 44</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>IC VALLE DEI LAGHI DRO</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cavedine, Piazza Italia</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>IC VALLE DEI LAGHI DRO</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>Drò, Via S. Antonio 17</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C35" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IC VALLE DEI LAGHI DRO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Vezzano, Via Roma (fermata farmacia)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>IS DON MILANI (Students staff)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rovereto, P.le Orsi – Fermata corriere davanti IPIA Veronesi</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>16</v>
       </c>
     </row>

--- a/tests/realSuite/Piano-Viaggi_Volley-S3_Tn-Nord-e-Sopramonte_4-dic-25_def3_con-VETTORE-e-CELL/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Volley-S3_Tn-Nord-e-Sopramonte_4-dic-25_def3_con-VETTORE-e-CELL/input.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ala, Via Betta 9</t>
+          <t>Scuola primaria "Abramo Betta", 9, Via Abramo Betta, Ala, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38061, Italia</t>
         </is>
       </c>
       <c r="C4" t="n">

--- a/tests/realSuite/Piano-Viaggi_Volley-S3_Tn-Nord-e-Sopramonte_4-dic-25_def3_con-VETTORE-e-CELL/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Volley-S3_Tn-Nord-e-Sopramonte_4-dic-25_def3_con-VETTORE-e-CELL/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC ALDENO MATTARELLO</t>
+          <t>IC BASSA ANAUNIA TUENNO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mattarello, Via Torre Franca (fermata bus "Al Parco")</t>
+          <t>Scuola secondaria di primo grado "V. Vielmetti" Denno, 3, Via Colle Verde, Anglar, Denno, Comunità della Val di Non, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38010, Italia</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -496,57 +496,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC ALTA VAL DI SOLE</t>
+          <t>IC BASSA ANAUNIA-TUENNO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ossana - SSPG - Via San Michele, 11</t>
+          <t>Tuenno - SSPG – V.le D'Anaunia, Via Maistrelli 11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC ARCO</t>
+          <t>IC BASSA VAL DI SOLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arco, park Foro Borio</t>
+          <t>Malé, Nuova stazione FTM</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC ARCO GARDA</t>
+          <t>IC CHIESE (cadetti)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arco, park Foro Borio</t>
+          <t>Pieve di Bono, Via Fiera 1 loc. Creto</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC AVIO</t>
+          <t>IC CLES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Avio, Viale A. Degasperi, 69</t>
+          <t>Cles, Piazza Fiera</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -556,12 +556,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC BASSA ANAUNIA TUENNO</t>
+          <t>IC FOLGARIA LAVARONE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tuenno - SSPG – V.le D'Anaunia, Via Maistrelli 11</t>
+          <t>Folgaria, park Palaghiaccio</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -571,12 +571,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC BASSA ANAUNIA-TUENNO</t>
+          <t>IC FOLGARIA LAVARONE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tuenno - SSPG – V.le D'Anaunia, Via Maistrelli 11</t>
+          <t>Lavarone, Frazione Gionghi, 107/6</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -586,12 +586,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC BASSA VAL DI SOLE</t>
+          <t>IC FONDO REVO'</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Malé, Nuova stazione FTM</t>
+          <t>Novella, Fermata Bus VVF, Via Canestrini</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -601,27 +601,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC CHIESE (cadetti)</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pieve di Bono, Via Fiera 1 loc. Creto</t>
+          <t>Comano Terme, Via San Giovanni Bosco 14</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC CLES</t>
+          <t>IC ISERA ROVERETO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cles, Piazza Fiera</t>
+          <t>Rovereto - Viale della Vittoria, 43</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -631,12 +631,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC FOLGARIA LAVARONE</t>
+          <t>IC LAVIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folgaria, park Palaghiaccio</t>
+          <t>Lavis, Via Sette 13/a</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -646,12 +646,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC FOLGARIA LAVARONE</t>
+          <t>IC MEZZOLOMBARDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lavarone, Frazione Gionghi, 107/6</t>
+          <t>Mezzolombardo, Via degli Alpini 17</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -661,27 +661,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC FONDO REVO'</t>
+          <t>IC MEZZOLOMBARDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Novella, Fermata Bus VVF, Via Canestrini</t>
+          <t>Spormaggiore, Via Alt Spaur, 5</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC GIUDICARIE ESTERIORI</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Comano Terme, Via San Giovanni Bosco 14</t>
+          <t>Pergine Valsugana, Via Caduti, 39</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -691,12 +691,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC ISERA ROVERETO</t>
+          <t>IC PRIMIERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rovereto - Viale della Vittoria, 43</t>
+          <t>USL Tonadico, Via Roma 1 – Primiero SMC</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -706,12 +706,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC LAVIS</t>
+          <t>IC RIVA 1 (cadetti)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lavis, Via Sette 13/a</t>
+          <t>Riva del Garda, piazzale centro Sportivo Malossini, Via delle Ginestre 3</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -721,42 +721,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO</t>
+          <t>IC RIVA 2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mezzolombardo, Via degli Alpini 17</t>
+          <t>Riva del Garda, piazzale centro Sportivo Malossini, Via delle Ginestre 3</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO</t>
+          <t>IC ROVERETO EST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Spormaggiore, Via Alt Spaur, 5</t>
+          <t>Rovereto, P.le Orsi – Fermata corriere davanti IPIA Veronesi</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC ROVERETO NORD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pergine Valsugana, Via Caduti, 39</t>
+          <t>Rovereto, P.le Orsi – Fermata corriere davanti IPIA Veronesi</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -766,210 +766,135 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IC PRIMIERO</t>
+          <t>IC ROVERETO SUD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USL Tonadico, Via Roma 1 – Primiero SMC</t>
+          <t>Rovereto, Parcheggio Ronchi</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC RIVA 1 (cadetti)</t>
+          <t>IC TAIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Riva del Garda, piazzale centro Sportivo Malossini, Via delle Ginestre 3</t>
+          <t>Coredo, Piazza della Chiesa</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC RIVA 2</t>
+          <t>IC TAIO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Riva del Garda, piazzale centro Sportivo Malossini, Via delle Ginestre 3</t>
+          <t>Taio, Piazza della Chiesa</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IC ROVERETO EST</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rovereto, P.le Orsi – Fermata corriere davanti IPIA Veronesi</t>
+          <t>Roncone, Via Nazionale 20</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IC ROVERETO NORD</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rovereto, P.le Orsi – Fermata corriere davanti IPIA Veronesi</t>
+          <t>Tione, Via Circonvalazione 44</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IC ROVERETO SUD</t>
+          <t>IC VALLE DEI LAGHI DRO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rovereto, Parcheggio Ronchi</t>
+          <t>Cavedine, Piazza Italia</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC VALLE DEI LAGHI DRO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Coredo, Piazza della Chiesa</t>
+          <t>Drò, Via S. Antonio 17</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC VALLE DEI LAGHI DRO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Taio, Piazza della Chiesa</t>
+          <t>Vezzano, Via Roma (fermata farmacia)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IS DON MILANI (Students staff)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Roncone, Via Nazionale 20</t>
+          <t>Rovereto, P.le Orsi – Fermata corriere davanti IPIA Veronesi</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>IC TIONE</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Tione, Via Circonvalazione 44</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>IC VALLE DEI LAGHI DRO</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Cavedine, Piazza Italia</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>IC VALLE DEI LAGHI DRO</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Drò, Via S. Antonio 17</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>IC VALLE DEI LAGHI DRO</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Vezzano, Via Roma (fermata farmacia)</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>IS DON MILANI (Students staff)</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Rovereto, P.le Orsi – Fermata corriere davanti IPIA Veronesi</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
         <v>16</v>
       </c>
     </row>
